--- a/Result/profitability/7791.xlsx
+++ b/Result/profitability/7791.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM12"/>
+  <dimension ref="A1:AM13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1954,6 +1954,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>7791</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>674</v>
+      </c>
+      <c r="D13" t="n">
+        <v>443</v>
+      </c>
+      <c r="E13" t="n">
+        <v>231</v>
+      </c>
+      <c r="F13" t="n">
+        <v>34.31</v>
+      </c>
+      <c r="G13" t="n">
+        <v>85</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>12.67%</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>89</v>
+      </c>
+      <c r="K13" t="n">
+        <v>67</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.30625</v>
+      </c>
+      <c r="N13" t="n">
+        <v>35.0225</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
+      </c>
+      <c r="V13" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.5508021390374331</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-1.549999999999997</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-0.04322364751812602</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>-0.4084507042253521</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-2.229999999999997</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>-0.06102900930487132</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
